--- a/astro-site/public/dl/bbq-catering-business-plan/bbq-catering-startup-checklist.xlsx
+++ b/astro-site/public/dl/bbq-catering-business-plan/bbq-catering-startup-checklist.xlsx
@@ -598,12 +598,12 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Choose your legal structure with your accountant: LLC or S corp</t>
+          <t>Hire an accountant or bookkeeper and set up quarterly estimated taxes</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Owner / Accountant</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>An LLC separates personal and business liability, which matters when you tow a smoker and cook with fire at other people's events. An S corp election can cut self-employment tax once profit is steady; ask your accountant when it pays off.</t>
+          <t>Ask for catering experience. Estimated taxes are due quarterly; move a share of every event deposit into a tax savings account so the bill never surprises you.</t>
         </is>
       </c>
     </row>
@@ -625,22 +625,22 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>File your LLC with the Secretary of State and appoint a registered agent</t>
+          <t>Choose your legal structure: an LLC, with or without an S corp election</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Owner / Attorney</t>
+          <t>Owner / Accountant</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>Weeks 1-2</t>
+          <t>Week 1</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>File the articles of organization online and sign an operating agreement, even for a single-member LLC. Fees and processing times vary by state; check your Secretary of State website.</t>
+          <t>An LLC separates personal and business liability, which matters when you tow a smoker and cook with fire at other people's events. An S corp election can cut self-employment tax once profit is steady; ask your accountant when it pays off.</t>
         </is>
       </c>
     </row>
@@ -652,22 +652,22 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Get your EIN from the IRS and register for state payroll and unemployment tax</t>
+          <t>File your LLC with the Secretary of State and appoint a registered agent</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Owner / Attorney</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Weeks 2-3</t>
+          <t>Weeks 1-2</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Apply once the state approves your LLC. The EIN is free and takes minutes at irs.gov. Register with your state workforce agency before your first hire, so your payroll provider can file from day one.</t>
+          <t>File the articles of organization online and sign an operating agreement, even for a single-member LLC. Fees and processing times vary by state; check your Secretary of State website.</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Open a business bank account and keep finances separate</t>
+          <t>Get your EIN from the IRS and register for state payroll and unemployment tax</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Bring your EIN letter and formation documents. Keep a card for purchases and a separate account for event deposits, so client money never mixes with personal money.</t>
+          <t>Apply once the state approves your LLC. The EIN is free and takes minutes at irs.gov. Register with your state workforce agency before your first hire, so your payroll provider can file from day one.</t>
         </is>
       </c>
     </row>
@@ -706,22 +706,22 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Get a seller's permit and register for state sales tax</t>
+          <t>Open a business bank account and keep finances separate</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Owner / Accountant</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Weeks 2-4</t>
+          <t>Weeks 2-3</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Apply on your state tax agency website. In many states sales tax applies to the whole catering invoice: smoked meats, staff and rentals, and in some states the service charge. Confirm your state's rule before you quote.</t>
+          <t>Bring your EIN letter and formation documents. Keep a card for purchases and a separate account for event deposits, so client money never mixes with personal money.</t>
         </is>
       </c>
     </row>
@@ -733,12 +733,12 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Apply for the city or county business license (and a DBA if you use a trade name)</t>
+          <t>Get a seller's permit and register for state sales tax</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Owner / Accountant</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Check every city where you plan to cater: some require their own license to operate there. A DBA (fictitious business name) is filed with the county clerk or the state, depending on where you are.</t>
+          <t>Apply on your state tax agency website. In many states sales tax applies to the whole catering invoice: smoked meats, staff and rentals, and in some states the service charge. Confirm your state's rule before you quote.</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Hire an accountant or bookkeeper and set up quarterly estimated taxes</t>
+          <t>Apply for the city or county business license (and a DBA if you use a trade name)</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Weeks 3-4</t>
+          <t>Weeks 2-4</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Ask for catering experience. Estimated taxes are due quarterly; move a share of every event deposit into a tax savings account so the bill never surprises you.</t>
+          <t>Check every city where you plan to cater: some require their own license to operate there. A DBA (fictitious business name) is filed with the county clerk or the state, depending on where you are.</t>
         </is>
       </c>
     </row>
@@ -787,22 +787,22 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Choose catering software for proposals, contracts, deposits and invoices</t>
+          <t>Take this plan to two lenders and apply for your loan (bank or SBA 7(a))</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Owner / Accountant</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Weeks 3-5</t>
+          <t>Weeks 3-6</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>One tool should send the quote, collect the e-signature and take the deposit by card or ACH. Run a mock proposal through it before you pay for a full year.</t>
+          <t>Bring the Word plan, the Excel projections and written quotes for the smoker trailer and the van. SBA 7(a) loans go through participating banks: ask what owner equity they expect and how long approval takes, and do not sign for the trailer until the loan is approved.</t>
         </is>
       </c>
     </row>
@@ -833,7 +833,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="119.75" customHeight="1">
+    <row r="14" ht="149.5" customHeight="1">
       <c r="A14" s="10" t="inlineStr">
         <is>
           <t>☐</t>
@@ -856,7 +856,7 @@
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Safe minimums (FDA Food Code): 145 °F for intact cuts, 155 °F for injected, tenderized or ground meat including sausage (an injected brisket counts), 165 °F for poultry, hot holding at 135 °F or higher. Cool to 70 °F within 2 hours and to 41 °F within a total of 6 hours; reheat to 165 °F. Tenderness temperatures for brisket are a quality target, not a safety limit.</t>
+          <t>Safe minimums (FDA Food Code): 145 °F (63 °C) for intact cuts, 155 °F (68 °C) for injected, tenderized or ground meat including sausage (an injected brisket counts), 165 °F (74 °C) for poultry, hot holding at 135 °F (57 °C) or higher. Cool to 70 °F (21 °C) within 2 hours and to 41 °F (5 °C) within a total of 6 hours; reheat to 165 °F (74 °C). Tenderness temperatures for brisket are a quality target, not a safety limit.</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Cooking with wood or charcoal usually needs a Class K plus 2A:10BC extinguisher, about 10 ft of clearance and limited propane on site (often up to 200 lb). Rules follow your city's fire code, so ask the fire marshal. Also ask venues about burn bans and cooking under tents.</t>
+          <t>Cooking with wood or charcoal usually needs a Class K plus 2A:10BC extinguisher, 10 ft between your pit and other vendors and limited propane on site (often up to 200 lb). Rules follow your city's fire code, so ask the fire marshal. Check your county's burn ban order before every event (some allow cooking in a closed smoker or grill, others do not) and ask venues about cooking under tents.</t>
         </is>
       </c>
     </row>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Register both at your state DMV in the business name. Commercial auto should cover the trailer; inland marine covers the smoker and gear in transit. A CDL is needed only at a gross vehicle weight rating of 26,001 lb or more.</t>
+          <t>Register both at your state DMV in the business name. Commercial auto should cover the trailer; inland marine covers the smoker and gear in transit. A CDL is needed only at 26,001 lb or more (pickup and trailer: a combined rating of 26,001 lb or more with a trailer over 10,000 lb). Towing across state lines above 10,000 lb combined may bring federal rules (USDOT number, DOT medical card): check with FMCSA.</t>
         </is>
       </c>
     </row>
@@ -1267,7 +1267,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="59.75" customHeight="1">
+    <row r="15" ht="89.75" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
         <is>
           <t>☐</t>
@@ -1285,12 +1285,12 @@
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Weeks 6-10</t>
+          <t>Weeks 3-5</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Required in almost every state once you have employees, including part-time event staff. Premiums depend on payroll and class code; cooks near open fire may be rated higher.</t>
+          <t>Required in almost every state once you have employees, including part-time event staff (Texas is the exception: optional there, but venues and lenders often ask for it). Premiums depend on payroll and class code; cooks near open fire may be rated higher.</t>
         </is>
       </c>
     </row>
@@ -1508,7 +1508,7 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Choose carriers that hold smoked meats at 135 °F or higher for the whole trip. Calibrate thermometers in ice water and keep spares in the van.</t>
+          <t>Choose carriers that hold smoked meats at 135 °F (57 °C) or higher for the whole trip. Calibrate thermometers in ice water and keep spares in the van.</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Buy carving station gear: board, knives, gloves and heat lamp</t>
+          <t>Open accounts with an approved-source meat supplier and a cash-and-carry</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -1584,12 +1584,12 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Weeks 4-6</t>
+          <t>Weeks 2-4</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>A carving station sells the show. Buy a stable board, two sharp slicing knives, cut-resistant gloves and a heat lamp, and script how you slice in front of guests.</t>
+          <t>Buy only from approved sources (USDA or state inspected), such as a broadline distributor or Restaurant Depot. A whole hog must never come from a custom exempt plant, since that meat is stamped not for sale. Compare delivery minimums and price lists.</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Open accounts with an approved-source meat supplier and a cash-and-carry</t>
+          <t>Buy carving station gear: board, knives, gloves and heat lamp</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Weeks 2-4</t>
+          <t>Weeks 4-6</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Buy only from approved sources (USDA or state inspected), such as a broadline distributor or Restaurant Depot. A whole hog must never come from a custom exempt plant, since that meat is stamped not for sale. Compare delivery minimums and price lists.</t>
+          <t>A carving station sells the show. Buy a stable board, two sharp slicing knives, cut-resistant gloves and a heat lamp, and script how you slice in front of guests.</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Use butcher paper, foil pans and sauce cups that survive heat. Use compostable items where your city requires them, and test that lids do not leak in a moving van.</t>
+          <t>Use butcher paper, foil pans and sauce cups that survive heat. Use compostable items where your city requires them, and test that lids do not leak in a moving van. Label each pan with the time it left hot holding and a discard time 4 hours later, or leave chafing dishes; ask your county whether it accepts time as a public health control (Food Code 3-501.19).</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>Place a logger in each hot box and in the van's cargo area. Save the report after every event as proof that food stayed at 135 °F or higher.</t>
+          <t>Place a logger in each hot box and in the van's cargo area. Save the report after every event as proof that food stayed at 135 °F (57 °C) or higher.</t>
         </is>
       </c>
     </row>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Share photos and short videos of the pit with the client's permission. Use text or SMS for quick client follow-ups; keep inquiries in your CRM.</t>
+          <t>Share photos and short videos of the pit with the client's permission. Use text messages for quick client follow-ups; keep inquiries in your CRM.</t>
         </is>
       </c>
     </row>
@@ -2538,7 +2538,7 @@
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>The calculator gives pounds of meat and price per guest, the smoke schedule and the shopping list; the template turns it into a polished quote. Log every inquiry and follow up within 48 hours.</t>
+          <t>The calculator gives pounds of meat and price per guest, the smoke schedule and the shopping list; the template turns it into a polished quote. Log every inquiry and follow up within 48 hours. Pick catering software that sends the quote, collects the e-signature and takes the deposit by card or ACH.</t>
         </is>
       </c>
     </row>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Hold the client briefing 3 weeks out: guests, package, allergies and timeline</t>
+          <t>Hold the final planning call with the client 3 weeks out: guests, package, allergies and timeline</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -2768,22 +2768,22 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Order meat 5-7 days out, then rub, trim and portion 1-2 days out</t>
+          <t>Collect the final balance before the event and invoice extras within 48 hours</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Pitmaster</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>5-7 days out, then 1-2 days out</t>
+          <t>Per contract, then within 48 hours</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Order raw pounds from the calculator against the final guest count, with a small buffer. Follow the smoke schedule (Start the pit by) and build one production list with who does what.</t>
+          <t>Collect the balance on the date in your contract (often 3 to 14 days before the event). Invoice overages within 48 hours and follow corporate invoices on their 30-day terms.</t>
         </is>
       </c>
     </row>
@@ -2795,22 +2795,22 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Probe, rest and hold the meat, then complete the loading and transport checklist</t>
+          <t>Order meat 5-7 days out, then rub, trim and portion 1-2 days out</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Pitmaster / Driver</t>
+          <t>Pitmaster</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>Day of event, before departure</t>
+          <t>5-7 days out, then 1-2 days out</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Hold at 135 °F or higher in hot boxes. Check carriers, pans, equipment and rentals against the list, and record food temperatures when you load and again when you arrive.</t>
+          <t>Order raw pounds from the calculator against the final guest count, with a small buffer. Follow the smoke schedule (Start the pit by) and build one production list with who does what.</t>
         </is>
       </c>
     </row>
@@ -2822,22 +2822,22 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Set up 60-90 minutes before service and run the carving station</t>
+          <t>Probe, rest and hold the meat, then complete the loading and transport checklist</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Event captain</t>
+          <t>Pitmaster / Driver</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Day of event</t>
+          <t>Day of event, before departure</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Arrive early, set up the buffet and check hot and cold temperatures before guests arrive. Run the live pit only where your permit and the venue allow it. Brief staff, then keep a service timeline.</t>
+          <t>Hold at 135 °F (57 °C) or higher in hot boxes. Check carriers, pans, equipment and rentals against the list, and record food temperatures when you load and again when you arrive.</t>
         </is>
       </c>
     </row>
@@ -2849,22 +2849,22 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Pick up, clean, cool the ash and return rentals</t>
+          <t>Set up 60-90 minutes before service and run the carving station</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Event captain / Event staff</t>
+          <t>Event captain</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Day of event or next morning</t>
+          <t>Day of event</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Count and inspect rentals before you leave. Make sure ash is cold and sealed in a metal container. Return rentals clean by the agreed time to avoid late fees.</t>
+          <t>Arrive early, set up the buffet and check hot and cold temperatures before guests arrive. Run the live pit only where your permit and the venue allow it. Brief staff, then keep a service timeline.</t>
         </is>
       </c>
     </row>
@@ -2876,22 +2876,22 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Collect the final balance before the event and invoice extras within 48 hours</t>
+          <t>Pick up, clean, cool the ash and return rentals</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Event captain / Event staff</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Per contract, then within 48 hours</t>
+          <t>Day of event or next morning</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Collect the balance on the date in your contract (often 3 to 14 days before the event). Invoice overages within 48 hours and follow corporate invoices on their 30-day terms.</t>
+          <t>Count and inspect rentals before you leave. Make sure ash is cold and sealed in a metal container. Return rentals clean by the agreed time to avoid late fees.</t>
         </is>
       </c>
     </row>
